--- a/reports/Debug-purgatory-20260105/Month to Date (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260105/Month to Date (Prior Year)_Visits.xlsx
@@ -34,9 +34,6 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
-  </si>
-  <si>
     <t>Purgatory Comp Tickets</t>
   </si>
   <si>
@@ -44,6 +41,9 @@
   </si>
   <si>
     <t>Purgatory Tickets</t>
+  </si>
+  <si>
+    <t>Purgatory Coaster</t>
   </si>
 </sst>
 </file>
@@ -437,7 +437,7 @@
         <v>45658</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>2027</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,13 +448,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C3" s="2">
-        <v>380</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,13 +462,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C4" s="2">
-        <v>684</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -479,10 +479,10 @@
         <v>45658</v>
       </c>
       <c r="C5" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -493,7 +493,7 @@
         <v>45659</v>
       </c>
       <c r="C6" s="2">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -507,10 +507,10 @@
         <v>45660</v>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>672</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,10 +518,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C8" s="2">
-        <v>487</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
@@ -532,10 +532,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C9" s="2">
-        <v>154</v>
+        <v>1965</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -546,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C10" s="2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -563,10 +563,10 @@
         <v>45658</v>
       </c>
       <c r="C11" s="2">
+        <v>2335</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -577,7 +577,7 @@
         <v>45659</v>
       </c>
       <c r="C12" s="2">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -591,10 +591,10 @@
         <v>45659</v>
       </c>
       <c r="C13" s="2">
-        <v>311</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,13 +602,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C14" s="2">
-        <v>2084</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C15" s="2">
-        <v>25</v>
+        <v>303</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -633,10 +633,10 @@
         <v>45661</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>1656</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -647,7 +647,7 @@
         <v>45662</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>45662</v>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -672,13 +672,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C19" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C20" s="2">
-        <v>1125</v>
+        <v>380</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>9</v>
@@ -703,10 +703,10 @@
         <v>45658</v>
       </c>
       <c r="C21" s="2">
-        <v>86</v>
+        <v>684</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C23" s="2">
-        <v>672</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -745,10 +745,10 @@
         <v>45660</v>
       </c>
       <c r="C24" s="2">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -759,10 +759,10 @@
         <v>45661</v>
       </c>
       <c r="C25" s="2">
-        <v>1965</v>
+        <v>487</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -773,7 +773,7 @@
         <v>45662</v>
       </c>
       <c r="C26" s="2">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -787,7 +787,7 @@
         <v>45658</v>
       </c>
       <c r="C27" s="2">
-        <v>2027</v>
+        <v>22</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C28" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -812,10 +812,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C29" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C30" s="2">
-        <v>1</v>
+        <v>311</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -843,10 +843,10 @@
         <v>45659</v>
       </c>
       <c r="C31" s="2">
-        <v>26</v>
+        <v>2084</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C32" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -868,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -882,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C34" s="2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C35" s="2">
-        <v>1871</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C36" s="2">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C37" s="2">
-        <v>26</v>
+        <v>1125</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C38" s="2">
-        <v>179</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,10 +952,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C39" s="2">
-        <v>6</v>
+        <v>712</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>6</v>
@@ -966,10 +966,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C40" s="2">
-        <v>4</v>
+        <v>1567</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -980,10 +980,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C41" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C42" s="2">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C43" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C44" s="2">
-        <v>1733</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1039,7 +1039,7 @@
         <v>45661</v>
       </c>
       <c r="C45" s="2">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C47" s="2">
-        <v>130</v>
+        <v>2295</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1081,7 +1081,7 @@
         <v>45662</v>
       </c>
       <c r="C48" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C49" s="2">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C50" s="2">
-        <v>712</v>
+        <v>1</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1123,7 +1123,7 @@
         <v>45659</v>
       </c>
       <c r="C51" s="2">
-        <v>1567</v>
+        <v>26</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1134,10 +1134,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C52" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C53" s="2">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1165,7 +1165,7 @@
         <v>45660</v>
       </c>
       <c r="C54" s="2">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,13 +1176,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C55" s="2">
-        <v>1</v>
+        <v>1871</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,10 +1190,10 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C56" s="2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1204,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C57" s="2">
-        <v>288</v>
+        <v>26</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C58" s="2">
-        <v>2295</v>
+        <v>179</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1232,13 +1232,13 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C59" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C60" s="2">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1263,10 +1263,10 @@
         <v>45658</v>
       </c>
       <c r="C61" s="2">
-        <v>2335</v>
+        <v>2</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C62" s="2">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1291,10 +1291,10 @@
         <v>45659</v>
       </c>
       <c r="C63" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1305,7 +1305,7 @@
         <v>45660</v>
       </c>
       <c r="C64" s="2">
-        <v>5</v>
+        <v>1733</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C65" s="2">
-        <v>303</v>
+        <v>101</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1333,10 +1333,10 @@
         <v>45661</v>
       </c>
       <c r="C66" s="2">
-        <v>1656</v>
+        <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C67" s="2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
@@ -1361,7 +1361,7 @@
         <v>45662</v>
       </c>
       <c r="C68" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>5</v>
